--- a/pipeline/credit_rating/output/visrating_xhtn_20260921.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260921.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-21 01:46:04</t>
+          <t>2026-09-21 09:15:37</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">

--- a/pipeline/credit_rating/output/visrating_xhtn_20260921.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260921.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-21 09:15:37</t>
+          <t>2026-09-21 10:07:06</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">

--- a/pipeline/credit_rating/output/visrating_xhtn_20260921.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260921.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q111"/>
+  <dimension ref="A1:Q113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,12 +510,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
+          <t>Công ty Cổ phần Tập đoàn Cơ khí Công nghệ Cao Siba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -526,12 +526,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -549,25 +549,29 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>SBG426001</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202609_phenikaa_rating_announcement_vn.175.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-sbg426001-21092026.177.html</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202609_phenikaa_rating_announcement_en.175.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-sbg426001-21092026.177.html</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-co-khi-cong-nghe-cao-siba.51.html</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>51</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -577,33 +581,33 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
-        <v>46281</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán LPS</t>
+          <t>Công ty Cổ phần Tập đoàn Cơ khí Công nghệ Cao Siba</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -627,16 +631,24 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-siba-high-tech-21092026.176.html</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-siba-high-tech-21092026.176.html</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-lps.42.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-co-khi-cong-nghe-cao-siba.51.html</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>51</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -646,28 +658,28 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>16/09/2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
+          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -687,7 +699,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -698,22 +710,22 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-tps-04092026.173.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202609_phenikaa_rating_announcement_vn.175.html</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-tps-04092026.173.html</t>
+          <t>https://visrating.com/rating-results/report/202609_phenikaa_rating_announcement_en.175.html</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -723,38 +735,38 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
-        <v>46269</v>
+        <v>46281</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
+          <t>Công ty Cổ phần Chứng khoán LPS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -764,7 +776,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -773,24 +785,16 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-26082026.172.html</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-26082026.172.html</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-lps.42.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -800,38 +804,38 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
-        <v>46260</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
+          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -841,7 +845,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -849,29 +853,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>BCML12601</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-bcm12601-24072026.171.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-tps-04092026.173.html</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-bcm12601-24072026.171.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-tps-04092026.173.html</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -881,22 +881,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
-        <v>46227</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
+          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -933,22 +933,22 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-becamex-24072026.170.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-26082026.172.html</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-becamex-24072026.170.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-26082026.172.html</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -958,22 +958,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
-        <v>46227</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Container Việt Nam</t>
+          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -1009,27 +1009,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>VSCL12601</t>
+          <t>BCML12601</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-23072026.169.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-bcm12601-24072026.171.html</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-23072026.169.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-bcm12601-24072026.171.html</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-container-viet-nam.50.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1039,22 +1039,22 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Container Việt Nam</t>
+          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1091,22 +1091,22 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-viconship-23072026.168.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-becamex-24072026.170.html</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-viconship-23072026.168.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-becamex-24072026.170.html</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-container-viet-nam.50.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1116,38 +1116,38 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán AIS</t>
+          <t>Công ty Cổ phần Container Việt Nam</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1165,25 +1165,29 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>VSCL12601</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-chung-khoan-ais-01072026.167.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-23072026.169.html</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-ais-securities-01072026.167.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-23072026.169.html</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-container-viet-nam.50.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>50</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1193,22 +1197,22 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
-        <v>46204</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Công ty TNHH Đầu tư StarBay Hà Nội</t>
+          <t>Công ty Cổ phần Container Việt Nam</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -1224,7 +1228,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1234,7 +1238,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1242,29 +1246,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>STA12601</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-24062026.165.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-viconship-23072026.168.html</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-24062026.165.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-viconship-23072026.168.html</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-dau-tu-starbay-ha-noi.49.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-container-viet-nam.50.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1274,38 +1274,38 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
-        <v>46197</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Nước Aqua One</t>
+          <t>Công ty Cổ phần Chứng khoán AIS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1323,21 +1323,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>AQ112501</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-chung-khoan-ais-01072026.167.html</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-ais-securities-01072026.167.html</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1347,11 +1351,11 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46197</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="13">
@@ -1362,7 +1366,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Nước Aqua One</t>
+          <t>Công ty TNHH Đầu tư StarBay Hà Nội</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1373,12 +1377,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1388,7 +1392,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1396,17 +1400,29 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>STA12601</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-24062026.165.html</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-24062026.165.html</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-dau-tu-starbay-ha-noi.49.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>49</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1416,7 +1432,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1431,7 +1447,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
+          <t>Công ty Cổ phần Nước Aqua One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
@@ -1447,7 +1463,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1457,7 +1473,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1465,17 +1481,21 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>AQ112501</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>33</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1485,7 +1505,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1495,12 +1515,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Công ty TNHH Đầu tư StarBay Hà Nội</t>
+          <t>Công ty Cổ phần Nước Aqua One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
@@ -1511,7 +1531,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1526,7 +1546,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1535,24 +1555,16 @@
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-starbay-23062026.159.html</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-starbay-23062026.159.html</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-dau-tu-starbay-ha-noi.49.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>33</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1562,22 +1574,22 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần VinaLiving Holdings</t>
+          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1603,7 +1615,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1616,12 +1628,12 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-vinaliving-holdings.40.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1631,33 +1643,33 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán BIDV</t>
+          <t>Công ty TNHH Đầu tư StarBay Hà Nội</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1672,7 +1684,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BB-</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1681,16 +1693,24 @@
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-starbay-23062026.159.html</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-starbay-23062026.159.html</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-bidv.39.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-dau-tu-starbay-ha-noi.49.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1700,22 +1720,22 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46190</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Công ty TNHH Greenland Phố Hoa</t>
+          <t>Công ty Cổ phần VinaLiving Holdings</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
@@ -1726,12 +1746,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1741,7 +1761,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1749,29 +1769,17 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>GPH12601</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-16062026.156.html</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-16062026.156.html</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-greenland-pho-hoa.48.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-vinaliving-holdings.40.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1781,33 +1789,33 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46189</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Công ty TNHH Greenland Phố Hoa</t>
+          <t>Công ty Cổ phần Chứng khoán BIDV</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1822,7 +1830,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>BB-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1831,24 +1839,16 @@
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-greenland-pho-hoa-16062026.155.html</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-greenland-pho-hoa-16062026.155.html</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-greenland-pho-hoa.48.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-bidv.39.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>39</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1858,11 +1858,11 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="20">
@@ -1873,23 +1873,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Thiên Việt</t>
+          <t>Công ty TNHH Greenland Phố Hoa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1907,17 +1907,29 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>GPH12601</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-16062026.156.html</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-16062026.156.html</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-cp-phan-chung-khoan-thien-viet.36.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-greenland-pho-hoa.48.html</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>48</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1927,7 +1939,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -1937,23 +1949,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
+          <t>Công ty TNHH Greenland Phố Hoa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1968,29 +1980,33 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>BB-</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-mcredit-11062026.153.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-greenland-pho-hoa-16062026.155.html</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-mcredit-11062026.153.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-greenland-pho-hoa-16062026.155.html</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tnhh-greenland-pho-hoa.48.html</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>48</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2000,33 +2016,33 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
-        <v>46184</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần TNG Land</t>
+          <t>Công ty Cổ phần Chứng khoán Thiên Việt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2041,7 +2057,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2050,24 +2066,16 @@
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-tng-land-10062026.152.html</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-tng-land-10062026.152.html</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tng-land.47.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-cp-phan-chung-khoan-thien-viet.36.html</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2077,33 +2085,33 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
-        <v>46183</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tổng Công ty Cổ phần Địa ốc Sài Gòn</t>
+          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2118,25 +2126,29 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>BBB+</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-mcredit-11062026.153.html</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-mcredit-11062026.153.html</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tong-cong-ty-co-phan-dia-oc-sai-gon.35.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2146,22 +2158,22 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco</t>
+          <t>Công ty Cổ phần TNG Land</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -2172,7 +2184,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2187,7 +2199,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2196,16 +2208,24 @@
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-tng-land-10062026.152.html</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-tng-land-10062026.152.html</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tng-land.47.html</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2215,28 +2235,28 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
-        <v>46177</v>
+        <v>46183</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VPBank</t>
+          <t>Công ty Cổ phần Tổng Công ty Cổ phần Địa ốc Sài Gòn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2256,7 +2276,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2269,12 +2289,12 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vpbank.23.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tong-cong-ty-co-phan-dia-oc-sai-gon.35.html</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2284,22 +2304,22 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
-        <v>46174</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Vận tải Dầu khí Thái Bình Dương</t>
+          <t>Công ty Cổ phần Tasco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -2310,7 +2330,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2325,7 +2345,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2334,24 +2354,16 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-pvtrans-pacific-25052026.146.html</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-pvtrans-pacific-25052026.146.html</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-van-tai-dau-khi-thai-binh-duong.43.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2361,22 +2373,22 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
-        <v>46167</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Chứng khoán VPBank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -2387,7 +2399,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2402,7 +2414,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2411,24 +2423,16 @@
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_tpb_rating_announcement_vn.137.html</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/202605_tpb_rating_announcement_en.137.html</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vpbank.23.html</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2438,33 +2442,33 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
-        <v>46164</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Vận tải Dầu khí Thái Bình Dương</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2479,7 +2483,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2488,16 +2492,24 @@
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-pvtrans-pacific-25052026.146.html</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/rating-announcement-pvtrans-pacific-25052026.146.html</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-van-tai-dau-khi-thai-binh-duong.43.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>43</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2507,22 +2519,22 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
-        <v>46163</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Phương Đông</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -2533,7 +2545,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2548,29 +2560,33 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>AA-</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-ocb-15052026.138.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_tpb_rating_announcement_vn.137.html</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-ocb-15052026.138.html</t>
+          <t>https://visrating.com/rating-results/report/202605_tpb_rating_announcement_en.137.html</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2580,33 +2596,33 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
-        <v>46157</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần FECON</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2621,7 +2637,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2630,24 +2646,16 @@
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_FECON_rating_annoucement_vn.118.html</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/202605_FECON_rating_annoucement_en.118.html</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-fecon.45.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2657,22 +2665,22 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
-        <v>46157</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
+          <t>Ngân hàng TMCP Phương Đông</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -2683,7 +2691,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2698,33 +2706,29 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_VND_rating_announcement_vn.80.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-ocb-15052026.138.html</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202605_VND_rating_announcement_en.80.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-ocb-15052026.138.html</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2734,17 +2738,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2765,7 +2769,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2783,19 +2787,15 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>FCN12601</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_FECON_bond_rating_announcement_vn.135.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_FECON_rating_annoucement_vn.118.html</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202605_FECON_bond_rating_announcement_en.135.html</t>
+          <t>https://visrating.com/rating-results/report/202605_FECON_rating_annoucement_en.118.html</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2815,22 +2815,22 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán MB</t>
+          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2867,22 +2867,22 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20260513_mbs_rating_announcement_vn-pdf.82.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_VND_rating_announcement_vn.80.html</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20260513_mbs_rating_announcement_vn-pdf.82.html</t>
+          <t>https://visrating.com/rating-results/report/202605_VND_rating_announcement_en.80.html</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2892,38 +2892,38 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán UP</t>
+          <t>Công ty Cổ phần FECON</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2933,29 +2933,37 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>BBB-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>FCN12601</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_ups_rating_announcement_vn.84.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_FECON_bond_rating_announcement_vn.135.html</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202605_ups_rating_announcement_en.84.html</t>
+          <t>https://visrating.com/rating-results/report/202605_FECON_bond_rating_announcement_en.135.html</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-fecon.45.html</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2965,22 +2973,22 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+          <t>Công ty Cổ phần Chứng khoán MB</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -3017,22 +3025,22 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_lpb_rating_announcement_vn-pdf.48.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20260513_mbs_rating_announcement_vn-pdf.82.html</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202605_lpb_rating_announcement_en-pdf.48.html</t>
+          <t>https://visrating.com/rating-results/report/20260513_mbs_rating_announcement_vn-pdf.82.html</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3042,33 +3050,33 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
-        <v>46150</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Công ty Cổ phần Chứng khoán UP</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3083,25 +3091,29 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Tích cực</t>
-        </is>
-      </c>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_ups_rating_announcement_vn.84.html</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202605_ups_rating_announcement_en.84.html</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3111,22 +3123,22 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
-        <v>46136</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -3137,7 +3149,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3152,29 +3164,33 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.113.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202605_lpb_rating_announcement_vn-pdf.48.html</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_vn.113.html</t>
+          <t>https://visrating.com/rating-results/report/202605_lpb_rating_announcement_en-pdf.48.html</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3184,38 +3200,38 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
-        <v>46134</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3225,33 +3241,25 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>VABCLH2330001</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.112.html</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_en.112.html</t>
-        </is>
-      </c>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Tích cực</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3261,11 +3269,11 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="39">
@@ -3292,7 +3300,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3306,19 +3314,15 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>VABCLH2431001</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.111.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.113.html</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_en.111.html</t>
+          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_vn.113.html</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3338,7 +3342,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3348,28 +3352,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco Auto</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3379,25 +3383,33 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>BBB+</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>VABCLH2330001</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.112.html</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_en.112.html</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco-auto.28.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3407,22 +3419,22 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP An Bình</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -3433,12 +3445,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3448,25 +3460,33 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>VABCLH2431001</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202604_vab_withdrawal_rating_announcement_vn.111.html</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202604_vab_withdrawal_rating_announcement_en.111.html</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3476,22 +3496,22 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tổng Công ty Dầu Việt Nam - Công ty Cổ phần</t>
+          <t>Công ty Cổ phần Tasco Auto</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
@@ -3502,7 +3522,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3517,7 +3537,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3526,24 +3546,16 @@
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-pvoil-16042026-SDq.119.html</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-pvoil-16042026-yDJ.119.html</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-dau-viet-nam-cong-ty-co-phan.38.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco-auto.28.html</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3553,28 +3565,28 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
-        <v>46128</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Dịch vụ Cáp treo Bà Nà</t>
+          <t>Ngân hàng TMCP An Bình</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3594,7 +3606,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3607,12 +3619,12 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-cap-treo-ba-na.24.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3622,33 +3634,33 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
-        <v>46122</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
+          <t>Tổng Công ty Dầu Việt Nam - Công ty Cổ phần</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nâng bậc</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3663,7 +3675,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3674,22 +3686,22 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/tps-bao-cao-ket-qua-xep-hang-tin-nhiem-20260408.114.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-pvoil-16042026-SDq.119.html</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/tps-rating-announcement-20260408.114.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-pvoil-16042026-yDJ.119.html</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-dau-viet-nam-cong-ty-co-phan.38.html</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>38</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3699,28 +3711,28 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
-        <v>46120</v>
+        <v>46128</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tổng công ty cổ phần Bảo hiểm Ngân hàng TMCP Công Thương Việt Nam</t>
+          <t>Công ty Cổ phần Dịch vụ Cáp treo Bà Nà</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3740,7 +3752,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3753,12 +3765,12 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-co-phan-bao-hiem-ngan-hang-tmcp-cong-thuong-viet-nam.22.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-cap-treo-ba-na.24.html</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -3768,22 +3780,22 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
-        <v>46115</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Sài Gòn - Hà Nội</t>
+          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -3794,7 +3806,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Nâng bậc</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3809,7 +3821,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3818,16 +3830,24 @@
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/tps-bao-cao-ket-qua-xep-hang-tin-nhiem-20260408.114.html</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/tps-rating-announcement-20260408.114.html</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-sai-gon-ha-noi.25.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -3837,28 +3857,28 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
-        <v>46114</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
+          <t>Tổng công ty cổ phần Bảo hiểm Ngân hàng TMCP Công Thương Việt Nam</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3878,7 +3898,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3891,12 +3911,12 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-co-phan-bao-hiem-ngan-hang-tmcp-cong-thuong-viet-nam.22.html</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -3906,22 +3926,22 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
-        <v>46107</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán LPS</t>
+          <t>Công ty Cổ phần Chứng khoán Sài Gòn - Hà Nội</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -3932,7 +3952,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3947,7 +3967,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3956,24 +3976,16 @@
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202603-lpbs-bao-cao-xhtn-pdf.109.html</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/202603-lpbs-rating-announcement-pdf.109.html</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-lps.42.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-sai-gon-ha-noi.25.html</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -3983,22 +3995,22 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
-        <v>46094</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>30/01/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
+          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -4037,12 +4049,12 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4052,22 +4064,22 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
-        <v>46052</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Cổ phần Chứng khoán LPS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -4078,12 +4090,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4093,33 +4105,33 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>VABLH2431002</t>
-        </is>
-      </c>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-tp-ket-thuc-xh-07012026-pdf.107.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202603-lpbs-bao-cao-xhtn-pdf.109.html</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-vab-bond-withdrawal-07012026-pdf.107.html</t>
+          <t>https://visrating.com/rating-results/report/202603-lpbs-rating-announcement-pdf.109.html</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-lps.42.html</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>42</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4129,22 +4141,22 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
-        <v>46029</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>30/01/2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -4155,7 +4167,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Thay đổi triển vọng</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4175,28 +4187,20 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tích cực</t>
+          <t>Ổn định</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20260106_gex_rating-announcement_vn-pdf.131.html</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/20260106_gex_rating-announcement_en-pdf.131.html</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4206,22 +4210,22 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
-        <v>46028</v>
+        <v>46052</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>31/12/2025</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán AIS</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -4232,12 +4236,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4247,25 +4251,33 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>A-</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>VABLH2431002</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-tp-ket-thuc-xh-07012026-pdf.107.html</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/visrating-vab-bond-withdrawal-07012026-pdf.107.html</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4275,22 +4287,22 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>24/12/2025</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Nước Aqua One</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -4301,12 +4313,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Thay đổi triển vọng</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -4316,37 +4328,33 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>AQ112501</t>
-        </is>
-      </c>
+          <t>Tích cực</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_aquaone_bond_rating_announcement_vn.143.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20260106_gex_rating-announcement_vn-pdf.131.html</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20251224_aquaone_bond_rating_announcement_en.143.html</t>
+          <t>https://visrating.com/rating-results/report/20260106_gex_rating-announcement_en-pdf.131.html</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4356,33 +4364,33 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
-        <v>46015</v>
+        <v>46028</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>24/12/2025</t>
+          <t>31/12/2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
+          <t>Công ty Cổ phần Chứng khoán AIS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4406,24 +4414,16 @@
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_thaco_rating_announcement_vn-pdf.100.html</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/20251224_thaco_rating_announcement_en-pdf.100.html</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4433,11 +4433,11 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="55">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4482,15 +4482,19 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>AQ112501</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_aquaone_rating_announcement_vn-pdf.98.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_aquaone_bond_rating_announcement_vn.143.html</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20251224_aquaone_rating_announcement_en-pdf.98.html</t>
+          <t>https://visrating.com/rating-results/report/20251224_aquaone_bond_rating_announcement_en.143.html</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4510,7 +4514,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4520,12 +4524,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>23/12/2025</t>
+          <t>24/12/2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần VinaLiving Holdings</t>
+          <t>Công ty Cổ phần Tập đoàn Trường Hải</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -4551,7 +4555,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4562,22 +4566,22 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/2025_vinaliving_rating_announcement_vn-pdf.97.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_thaco_rating_announcement_vn-pdf.100.html</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/2025_vinaliving_rating_announcement_en-pdf.97.html</t>
+          <t>https://visrating.com/rating-results/report/20251224_thaco_rating_announcement_en-pdf.100.html</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-vinaliving-holdings.40.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-truong-hai.41.html</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4587,28 +4591,28 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17/12/2025</t>
+          <t>24/12/2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán BIDV</t>
+          <t>Công ty Cổ phần Nước Aqua One</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4628,7 +4632,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4639,22 +4643,22 @@
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202512-bsi-bao-cao-xhtn-pdf.93.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251224_aquaone_rating_announcement_vn-pdf.98.html</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202512-bsi-rating-announcement-pdf.93.html</t>
+          <t>https://visrating.com/rating-results/report/20251224_aquaone_rating_announcement_en-pdf.98.html</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-bidv.39.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-nuoc-aqua-one.33.html</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>33</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4664,28 +4668,28 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
-        <v>46008</v>
+        <v>46015</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>23/12/2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Thiên Việt</t>
+          <t>Công ty Cổ phần VinaLiving Holdings</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4705,7 +4709,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4716,22 +4720,22 @@
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-tvs-bao-cao-kqxhtn-16122025vn-pdf.92.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/2025_vinaliving_rating_announcement_vn-pdf.97.html</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-tvs-rating-announcement-16122025en-pdf.92.html</t>
+          <t>https://visrating.com/rating-results/report/2025_vinaliving_rating_announcement_en-pdf.97.html</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-cp-phan-chung-khoan-thien-viet.36.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-vinaliving-holdings.40.html</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -4741,22 +4745,22 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
-        <v>46007</v>
+        <v>46014</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Cổ phần Chứng khoán BIDV</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -4767,12 +4771,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4782,7 +4786,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4790,21 +4794,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>VABLH2431002</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202512-bsi-bao-cao-xhtn-pdf.93.html</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202512-bsi-rating-announcement-pdf.93.html</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-bidv.39.html</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>39</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -4814,22 +4822,22 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
-        <v>46003</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Cổ phần Chứng khoán Thiên Việt</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -4840,12 +4848,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4855,7 +4863,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4863,21 +4871,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>VABCLH2330001</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-tvs-bao-cao-kqxhtn-16122025vn-pdf.92.html</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/visrating-tvs-rating-announcement-16122025en-pdf.92.html</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-cp-phan-chung-khoan-thien-viet.36.html</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -4887,11 +4899,11 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
     </row>
     <row r="61">
@@ -4902,7 +4914,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -4918,7 +4930,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4928,7 +4940,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4936,17 +4948,21 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>VABLH2431002</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4956,7 +4972,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5007,7 +5023,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>VABCLH2431001</t>
+          <t>VABCLH2330001</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -5029,7 +5045,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5039,23 +5055,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco</t>
+          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5070,7 +5086,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5079,24 +5095,16 @@
         </is>
       </c>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202512_hut_rating_announcement_vn-pdf.91.html</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/202512_hut_rating_announcement_en-pdf.91.html</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5106,28 +5114,28 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
-        <v>46000</v>
+        <v>46003</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5137,7 +5145,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5155,17 +5163,21 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>VABCLH2431001</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5175,22 +5187,22 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
-        <v>45996</v>
+        <v>46003</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tổng Công ty Cổ phần Địa ốc Sài Gòn</t>
+          <t>Công ty Cổ phần Tasco</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -5201,7 +5213,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5227,22 +5239,22 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/2025_sgr_rating_announcement_vn-pdf.89.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202512_hut_rating_announcement_vn-pdf.91.html</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/2025_sgr_rating_announcement_en-pdf.89.html</t>
+          <t>https://visrating.com/rating-results/report/202512_hut_rating_announcement_en-pdf.91.html</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tong-cong-ty-co-phan-dia-oc-sai-gon.35.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5252,33 +5264,33 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VPBank</t>
+          <t>Công ty Cổ phần Tasco</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -5293,7 +5305,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5302,24 +5314,16 @@
         </is>
       </c>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202511-rating-announcement-vpbanks-vn-pdf.88.html</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/202511-rating-announcement-vpbanks-en-pdf.88.html</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vpbank.23.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5329,33 +5333,33 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
-        <v>45992</v>
+        <v>45996</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Tổng Công ty Cổ phần Địa ốc Sài Gòn</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5370,7 +5374,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5379,16 +5383,24 @@
         </is>
       </c>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/2025_sgr_rating_announcement_vn-pdf.89.html</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/2025_sgr_rating_announcement_en-pdf.89.html</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tong-cong-ty-co-phan-dia-oc-sai-gon.35.html</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5398,22 +5410,22 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
-        <v>45982</v>
+        <v>45996</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
+          <t>Công ty Cổ phần Chứng khoán VPBank</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -5424,7 +5436,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5439,7 +5451,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5448,16 +5460,24 @@
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202511-rating-announcement-vpbanks-vn-pdf.88.html</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/202511-rating-announcement-vpbanks-en-pdf.88.html</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vpbank.23.html</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5467,22 +5487,22 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
-        <v>45975</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán UP</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -5508,7 +5528,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5521,12 +5541,12 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5536,11 +5556,11 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
-        <v>45975</v>
+        <v>45982</v>
       </c>
     </row>
     <row r="70">
@@ -5551,7 +5571,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán MB</t>
+          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -5577,7 +5597,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5590,12 +5610,12 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5605,7 +5625,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5620,7 +5640,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Phương Đông</t>
+          <t>Công ty Cổ phần Chứng khoán UP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -5646,7 +5666,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -5659,12 +5679,12 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -5674,7 +5694,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5684,12 +5704,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08/11/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+          <t>Công ty Cổ phần Chứng khoán MB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -5728,12 +5748,12 @@
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -5743,28 +5763,28 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
-        <v>45969</v>
+        <v>45975</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24/10/2025</t>
+          <t>14/11/2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Ngân hàng TMCP Phương Đông</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5784,7 +5804,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5797,12 +5817,12 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -5812,22 +5832,22 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
-        <v>45954</v>
+        <v>45975</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>08/11/2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP An Bình</t>
+          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -5838,7 +5858,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5853,7 +5873,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5862,24 +5882,16 @@
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251022_abb_rating_announcement_vn-pdf.78.html</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/20251022_abb_rating_announcement_en-pdf.78.html</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -5889,28 +5901,28 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
-        <v>45952</v>
+        <v>45969</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>22/10/2025</t>
+          <t>24/10/2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5930,7 +5942,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5943,12 +5955,12 @@
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -5958,33 +5970,33 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>21/10/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco Auto</t>
+          <t>Ngân hàng TMCP An Bình</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5999,7 +6011,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6010,22 +6022,22 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/251020_tasco-auto_rating_announcement_vn-pdf.76.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251022_abb_rating_announcement_vn-pdf.78.html</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202510_tasco-auto_rating_announcement_en-pdf.76.html</t>
+          <t>https://visrating.com/rating-results/report/20251022_abb_rating_announcement_en-pdf.78.html</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco-auto.28.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6035,22 +6047,22 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>22/10/2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tổng công ty cổ phần Bảo hiểm Ngân hàng TMCP Công Thương Việt Nam</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -6061,7 +6073,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6076,7 +6088,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6085,24 +6097,16 @@
         </is>
       </c>
       <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_vbi_bao_cao_ket_qua_xhtn_03102025-pdf.66.html</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/visrating_vbi_rating_announcement_03102025-pdf.66.html</t>
-        </is>
-      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-co-phan-bao-hiem-ngan-hang-tmcp-cong-thuong-viet-nam.22.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6112,28 +6116,28 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
-        <v>45933</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>21/10/2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Sài Gòn - Hà Nội</t>
+          <t>Công ty Cổ phần Tasco Auto</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6153,7 +6157,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6164,22 +6168,22 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251002-shs-bao-cao-xhtn-pdf.65.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/251020_tasco-auto_rating_announcement_vn-pdf.76.html</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20251002-shs-rating-announcement-en-pdf.65.html</t>
+          <t>https://visrating.com/rating-results/report/202510_tasco-auto_rating_announcement_en-pdf.76.html</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-sai-gon-ha-noi.25.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco-auto.28.html</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6189,28 +6193,28 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
-        <v>45932</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>26/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Dịch vụ Cáp treo Bà Nà</t>
+          <t>Tổng công ty cổ phần Bảo hiểm Ngân hàng TMCP Công Thương Việt Nam</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6230,7 +6234,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -6241,22 +6245,22 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250926_bnc_rating_announcement_vn-pdf.64.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_vbi_bao_cao_ket_qua_xhtn_03102025-pdf.66.html</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250926_bnc_rating_announcement_en-pdf.64.html</t>
+          <t>https://visrating.com/rating-results/report/visrating_vbi_rating_announcement_03102025-pdf.66.html</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-cap-treo-ba-na.24.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tong-cong-ty-co-phan-bao-hiem-ngan-hang-tmcp-cong-thuong-viet-nam.22.html</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6266,33 +6270,33 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
-        <v>45926</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>16/09/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
+          <t>Công ty Cổ phần Chứng khoán Sài Gòn - Hà Nội</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6318,22 +6322,22 @@
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202509_phenikaa_rating_announcement_vn-pdf.63.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20251002-shs-bao-cao-xhtn-pdf.65.html</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/202509_phenikaa_rating_announcement_en-pdf.63.html</t>
+          <t>https://visrating.com/rating-results/report/20251002-shs-rating-announcement-en-pdf.65.html</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-sai-gon-ha-noi.25.html</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6343,28 +6347,28 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
-        <v>45916</v>
+        <v>45932</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>05/09/2025</t>
+          <t>26/09/2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
+          <t>Công ty Cổ phần Dịch vụ Cáp treo Bà Nà</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6384,7 +6388,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6395,22 +6399,22 @@
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250905-tps-bao-cao-xhtn-pdf.62.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250926_bnc_rating_announcement_vn-pdf.64.html</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250905-tps-rating-announcement-pdf.62.html</t>
+          <t>https://visrating.com/rating-results/report/20250926_bnc_rating_announcement_en-pdf.64.html</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-cap-treo-ba-na.24.html</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6420,22 +6424,22 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
-        <v>45905</v>
+        <v>45926</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>01/08/2025</t>
+          <t>16/09/2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
+          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -6446,7 +6450,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6472,22 +6476,22 @@
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250801_bcm_rating_announcement_vn-pdf.61.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/202509_phenikaa_rating_announcement_vn-pdf.63.html</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250801_bcm_rating_announcement_en-pdf.61.html</t>
+          <t>https://visrating.com/rating-results/report/202509_phenikaa_rating_announcement_en-pdf.63.html</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6497,22 +6501,22 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
-        <v>45870</v>
+        <v>45916</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>05/09/2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán AIS</t>
+          <t>Công ty Cổ phần Chứng khoán Tiên Phong</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -6538,7 +6542,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -6549,22 +6553,22 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250701_ais_rating_announcement_vn-pdf.59.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250905-tps-bao-cao-xhtn-pdf.62.html</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250701_ais_rating_announcement_en-pdf.59.html</t>
+          <t>https://visrating.com/rating-results/report/20250905-tps-rating-announcement-pdf.62.html</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tien-phong-securities-corporation.21.html</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -6574,28 +6578,28 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
-        <v>45839</v>
+        <v>45905</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>01/08/2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Tập đoàn Đầu tư và Phát triển Công nghiệp Becamex - CTCP</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6605,7 +6609,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6615,7 +6619,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -6623,29 +6627,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>VABCLH2330001</t>
-        </is>
-      </c>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.145.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250801_bcm_rating_announcement_vn-pdf.61.html</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.145.html</t>
+          <t>https://visrating.com/rating-results/report/20250801_bcm_rating_announcement_en-pdf.61.html</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/tap-doan-dau-tu-va-phat-trien-cong-nghiep-becamex-ctcp.19.html</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -6655,22 +6655,22 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
-        <v>45820</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>12/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Công ty Cổ phần Chứng khoán AIS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Công cụ nợ</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6704,29 +6704,25 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>VABCLH2431001</t>
-        </is>
-      </c>
+      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.144.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250701_ais_rating_announcement_vn-pdf.59.html</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.144.html</t>
+          <t>https://visrating.com/rating-results/report/20250701_ais_rating_announcement_en-pdf.59.html</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-ais.18.html</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -6736,11 +6732,11 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
-        <v>45820</v>
+        <v>45839</v>
       </c>
     </row>
     <row r="86">
@@ -6787,17 +6783,17 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>VABLH2431002</t>
+          <t>VABCLH2330001</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.58.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.145.html</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.58.html</t>
+          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.145.html</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -6817,7 +6813,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6832,7 +6828,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -6848,7 +6844,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6858,7 +6854,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6866,25 +6862,29 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>VABCLH2431001</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250612-rating-announcement-mcredit-vn-pdf.55.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.144.html</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250612-rating-announcement-mcredit-en-pdf.55.html</t>
+          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.144.html</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6904,28 +6904,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>04/06/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Công cụ nợ</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6943,17 +6943,29 @@
           <t>Ổn định</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>VABLH2431002</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-trai-phieu-kqxhtn-12062025vn.58.html</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/visrating-vab-bond-announcement-12062025en.58.html</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -6963,33 +6975,33 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
-        <v>45812</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>29/05/2025</t>
+          <t>12/06/2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
+          <t>Công ty Tài chính tín dụng tiêu dùng TNHH MB Shinsei</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kết thúc</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7004,29 +7016,33 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>WR</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250529-ha-an-rating-withdrawal-vn-pdf.54.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250612-rating-announcement-mcredit-vn-pdf.55.html</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250529_ha_an_rating_withdrawal-en-pdf.54.html</t>
+          <t>https://visrating.com/rating-results/report/20250612-rating-announcement-mcredit-en-pdf.55.html</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-tai-chinh-tin-dung-tieu-dung-tnhh-mb-shinsei.17.html</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7036,33 +7052,33 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
-        <v>45806</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>21/05/2025</t>
+          <t>04/06/2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Tasco</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7077,7 +7093,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7086,24 +7102,16 @@
         </is>
       </c>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_tpb_bao_cao_ket_qua_xhtn_21052025-pdf.53.html</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/visrating_tpb_rating_announcement_21052025-pdf.53.html</t>
-        </is>
-      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7113,33 +7121,33 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
-        <v>45798</v>
+        <v>45812</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>29/05/2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán MB</t>
+          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Kết thúc</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7154,33 +7162,29 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>A+</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Ổn định</t>
-        </is>
-      </c>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_mbs_bao_cao_ket_qua_xhtn_15052025-pdf.52.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250529-ha-an-rating-withdrawal-vn-pdf.54.html</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating_mbs_rating_announcement_15052025-pdf.52.html</t>
+          <t>https://visrating.com/rating-results/report/20250529_ha_an_rating_withdrawal-en-pdf.54.html</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -7190,22 +7194,22 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
-        <v>45792</v>
+        <v>45806</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>15/05/2025</t>
+          <t>21/05/2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán UP</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -7216,7 +7220,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7231,7 +7235,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>BBB-</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -7242,22 +7246,22 @@
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-ups-bao-cao-ket-qua-xhtn-15052025-pdf.51.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_tpb_bao_cao_ket_qua_xhtn_21052025-pdf.53.html</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-ups-rating-announcement-15052025-pdf.51.html</t>
+          <t>https://visrating.com/rating-results/report/visrating_tpb_rating_announcement_21052025-pdf.53.html</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -7267,11 +7271,11 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
-        <v>45792</v>
+        <v>45798</v>
       </c>
     </row>
     <row r="93">
@@ -7282,7 +7286,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Phương Đông</t>
+          <t>Công ty Cổ phần Chứng khoán MB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -7293,7 +7297,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cập nhật</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7308,7 +7312,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -7319,22 +7323,22 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-ocb-bao-cao-ket-qua-xhtn-15052025-pdf.50.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating_mbs_bao_cao_ket_qua_xhtn_15052025-pdf.52.html</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-ocb-rating-announcement-15052025-pdf.50.html</t>
+          <t>https://visrating.com/rating-results/report/visrating_mbs_rating_announcement_15052025-pdf.52.html</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-mb.15.html</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -7344,7 +7348,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7354,12 +7358,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>14/05/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
+          <t>Công ty Cổ phần Chứng khoán UP</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -7385,7 +7389,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>BBB-</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7396,22 +7400,22 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250624_vnd_rating_announcement_vn-pdf.49.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-ups-bao-cao-ket-qua-xhtn-15052025-pdf.51.html</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/20250624_vnd_rating_announcement_en-pdf.49.html</t>
+          <t>https://visrating.com/rating-results/report/visrating-ups-rating-announcement-15052025-pdf.51.html</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-up.14.html</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -7421,22 +7425,22 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>45791</v>
+        <v>45792</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>08/05/2025</t>
+          <t>15/05/2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+          <t>Ngân hàng TMCP Phương Đông</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -7462,7 +7466,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7473,22 +7477,22 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-lpbank-08052025.140.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-ocb-bao-cao-ket-qua-xhtn-15052025-pdf.50.html</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/rating-announcement-lpbank-08052025.140.html</t>
+          <t>https://visrating.com/rating-results/report/visrating-ocb-rating-announcement-15052025-pdf.50.html</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -7498,33 +7502,33 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
-        <v>45785</v>
+        <v>45792</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>25/04/2025</t>
+          <t>14/05/2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Công ty Cổ phần Chứng khoán VNDIRECT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7539,7 +7543,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7548,16 +7552,24 @@
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/20250624_vnd_rating_announcement_vn-pdf.49.html</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/20250624_vnd_rating_announcement_en-pdf.49.html</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-chung-khoan-vndirect.13.html</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -7567,22 +7579,22 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
-        <v>45772</v>
+        <v>45791</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>22/04/2025</t>
+          <t>08/05/2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Việt Á</t>
+          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -7593,7 +7605,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Cập nhật</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7608,7 +7620,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7619,22 +7631,22 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-bao-cao-kqxhtn-22042025vn-pdf.134.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-lpbank-08052025.140.html</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/visrating-vab-rating-announcement-22042025en-pdf.134.html</t>
+          <t>https://visrating.com/rating-results/report/rating-announcement-lpbank-08052025.140.html</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -7644,28 +7656,28 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
-        <v>45769</v>
+        <v>45785</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>21/04/2025</t>
+          <t>25/04/2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP An Bình</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -7685,7 +7697,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7698,12 +7710,12 @@
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -7713,33 +7725,33 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
-        <v>45768</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>16/03/2025</t>
+          <t>22/04/2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
+          <t>Ngân hàng TMCP Việt Á</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7754,7 +7766,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7763,16 +7775,24 @@
         </is>
       </c>
       <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/visrating-vab-bao-cao-kqxhtn-22042025vn-pdf.134.html</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/visrating-vab-rating-announcement-22042025en-pdf.134.html</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-viet-a.12.html</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -7782,33 +7802,33 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
-        <v>45732</v>
+        <v>45769</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>04/12/2024</t>
+          <t>21/04/2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tasco</t>
+          <t>Ngân hàng TMCP An Bình</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7823,7 +7843,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>BBB+</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7832,24 +7852,16 @@
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-hut-bao-cao-ket-qua-xhtn-04122024-pdf.44.html</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-hut-rating-announcement-04122024-pdf.44.html</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -7859,22 +7871,22 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
-        <v>45630</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>29/11/2024</t>
+          <t>16/03/2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
+          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -7900,7 +7912,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -7913,12 +7925,12 @@
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -7928,33 +7940,33 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
-        <v>45625</v>
+        <v>45732</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>21/11/2024</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Tasco</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Giám sát theo dõi</t>
+          <t>Xếp hạng lần đầu</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7969,7 +7981,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>BBB+</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7978,16 +7990,24 @@
         </is>
       </c>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-hut-bao-cao-ket-qua-xhtn-04122024-pdf.44.html</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/vis-rating-hut-rating-announcement-04122024-pdf.44.html</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tasco.8.html</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -7997,28 +8017,28 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
-        <v>45617</v>
+        <v>45630</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15/11/2024</t>
+          <t>29/11/2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Phương Đông</t>
+          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8038,7 +8058,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -8051,12 +8071,12 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8066,22 +8086,22 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
-        <v>45611</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>08/11/2024</t>
+          <t>21/11/2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -8107,7 +8127,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -8120,12 +8140,12 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8135,33 +8155,33 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
-        <v>45604</v>
+        <v>45617</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>25/10/2024</t>
+          <t>15/11/2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Gelex</t>
+          <t>Ngân hàng TMCP Phương Đông</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8176,7 +8196,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8185,24 +8205,16 @@
         </is>
       </c>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-gex-bao-cao-ket-qua-xep-hang-tin-nhiem-25102024-pdf.35.html</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-gex-rating-announcement-25102024-pdf.35.html</t>
-        </is>
-      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8212,22 +8224,22 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
-        <v>45590</v>
+        <v>45611</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21/10/2024</t>
+          <t>08/11/2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP An Bình</t>
+          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -8238,7 +8250,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Xếp hạng lần đầu</t>
+          <t>Giám sát theo dõi</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8253,7 +8265,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -8262,24 +8274,16 @@
         </is>
       </c>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-abb-bao-cao-ket-qua-xep-hang-tin-nhiem-21102024-pdf.32.html</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-abb-rating-announcement-21102024-pdf.32.html</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8289,22 +8293,22 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
-        <v>45586</v>
+        <v>45604</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>16/09/2024</t>
+          <t>25/10/2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
+          <t>Công ty Cổ phần Tập đoàn Gelex</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -8341,22 +8345,22 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-phenikaa-bao-cao-ket-qua-xep-hang-tin-nhiem-16092024-pdf.31.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-gex-bao-cao-ket-qua-xep-hang-tin-nhiem-25102024-pdf.35.html</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-phenikaa-rating-announcement-16092024-pdf.31.html</t>
+          <t>https://visrating.com/rating-results/report/vis-rating-gex-rating-announcement-25102024-pdf.35.html</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-gelex.7.html</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8366,28 +8370,28 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
-        <v>45551</v>
+        <v>45590</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>29/05/2024</t>
+          <t>21/10/2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
+          <t>Ngân hàng TMCP An Bình</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Doanh nghiệp</t>
+          <t>Định chế tài chính</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8407,7 +8411,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>BBB</t>
+          <t>A-</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8418,22 +8422,22 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-ha-an-bao-cao-ket-qua-xep-hang-tin-nhiem-29052024-pdf.26.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-abb-bao-cao-ket-qua-xep-hang-tin-nhiem-21102024-pdf.32.html</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-ha-an-rating-announcement-29052024-pdf.26.html</t>
+          <t>https://visrating.com/rating-results/report/vis-rating-abb-rating-announcement-21102024-pdf.32.html</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-an-binh.6.html</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -8443,28 +8447,28 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
-        <v>45441</v>
+        <v>45586</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>21/05/2024</t>
+          <t>16/09/2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Tiên Phong</t>
+          <t>Công ty Cổ phần Tập đoàn Phượng Hoàng Xanh A&amp;A</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8484,7 +8488,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8495,22 +8499,22 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-tpb-bao-cao-ket-qua-xep-hang-tin-nhiem-21052024-pdf.25.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-phenikaa-bao-cao-ket-qua-xep-hang-tin-nhiem-16092024-pdf.31.html</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-tpb-rating-announcement-21052024-pdf.25.html</t>
+          <t>https://visrating.com/rating-results/report/vis-rating-phenikaa-rating-announcement-16092024-pdf.31.html</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-tap-doan-phuong-hoang-xanh-aanda.5.html</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -8520,28 +8524,28 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
-        <v>45433</v>
+        <v>45551</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15/05/2024</t>
+          <t>29/05/2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Phương Đông</t>
+          <t>Công ty Cổ phần Đầu tư Kinh doanh Bất động sản Hà An</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Định chế tài chính</t>
+          <t>Doanh nghiệp</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8561,7 +8565,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8572,22 +8576,22 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-ocb-bao-cao-ket-qua-xep-hang-tin-nhiem-15052024-pdf.24.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-ha-an-bao-cao-ket-qua-xep-hang-tin-nhiem-29052024-pdf.26.html</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>https://visrating.com/rating-results/report/vis-rating-ocb-rating-announcement-15052024-pdf.24.html</t>
+          <t>https://visrating.com/rating-results/report/vis-rating-ha-an-rating-announcement-29052024-pdf.26.html</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/cong-ty-co-phan-dau-tu-kinh-doanh-bat-dong-san-ha-an.1.html</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O110" t="inlineStr">
@@ -8597,22 +8601,22 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-21 10:07:06</t>
+          <t>2026-09-21 15:17:27</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
-        <v>45427</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>08/05/2024</t>
+          <t>21/05/2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+          <t>Ngân hàng TMCP Tiên Phong</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -8638,7 +8642,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8649,35 +8653,189 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-tpb-bao-cao-ket-qua-xep-hang-tin-nhiem-21052024-pdf.25.html</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/vis-rating-tpb-rating-announcement-21052024-pdf.25.html</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-tien-phong.4.html</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>VIS Rating</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:17:27</t>
+        </is>
+      </c>
+      <c r="Q111" s="1" t="n">
+        <v>45433</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>15/05/2024</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Phương Đông</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Định chế tài chính</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Xếp hạng lần đầu</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Dài hạn</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/vis-rating-ocb-bao-cao-ket-qua-xep-hang-tin-nhiem-15052024-pdf.24.html</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>https://visrating.com/rating-results/report/vis-rating-ocb-rating-announcement-15052024-pdf.24.html</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-phuong-dong.3.html</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>VIS Rating</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:17:27</t>
+        </is>
+      </c>
+      <c r="Q112" s="1" t="n">
+        <v>45427</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>08/05/2024</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ngân hàng TMCP Lộc Phát Việt Nam</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Định chế tài chính</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Xếp hạng lần đầu</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Dài hạn</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Ổn định</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
           <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/bao-cao/bao-cao-ket-qua-xep-hang-tin-nhiem-lpbank-08052024.139.html</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t>https://visrating.com/rating-results/report/rating-announcement-lpbank-08052024.139.html</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>https://visrating.com/ket-qua-xep-hang-tin-nhiem/to-chuc/ngan-hang-tmcp-loc-phat-viet-nam.2.html</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
+      <c r="N113" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>VIS Rating</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>2026-09-21 10:07:06</t>
-        </is>
-      </c>
-      <c r="Q111" s="1" t="n">
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>VIS Rating</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>2026-09-21 15:17:27</t>
+        </is>
+      </c>
+      <c r="Q113" s="1" t="n">
         <v>45420</v>
       </c>
     </row>
